--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:47</t>
+    <t xml:space="preserve">2026-09-09 22:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:35</t>
+    <t xml:space="preserve">2026-09-12 19:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_tarapaca.xlsx
@@ -39,24 +39,24 @@
     <t xml:space="preserve">Colchane</t>
   </si>
   <si>
+    <t xml:space="preserve">Camiña</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alto Hospicio</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pica</t>
   </si>
   <si>
-    <t xml:space="preserve">Camiña</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alto Hospicio</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pozo Almonte</t>
   </si>
   <si>
+    <t xml:space="preserve">Iquique</t>
+  </si>
+  <si>
     <t xml:space="preserve">Huara</t>
   </si>
   <si>
-    <t xml:space="preserve">Iquique</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:51</t>
+    <t xml:space="preserve">2026-09-24 00:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -502,7 +502,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>32.08</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="3">
@@ -513,13 +513,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>6.49</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="4">
@@ -530,13 +530,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1402</v>
+        <v>1107</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.57</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="5">
@@ -547,13 +547,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1107</v>
+        <v>1405</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.33</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="6">
@@ -570,7 +570,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.07</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="7">
@@ -581,13 +581,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1404</v>
+        <v>1101</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.47</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="8">
@@ -598,13 +598,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1101</v>
+        <v>1404</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-6.52</v>
+        <v>-2.89</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:30</t>
+    <t xml:space="preserve">2026-09-27 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -502,7 +502,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>19.89</v>
+        <v>198.87</v>
       </c>
     </row>
     <row r="3">
@@ -519,7 +519,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2.27</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="4">
@@ -536,7 +536,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1.27</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="5">
@@ -553,7 +553,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.95</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="6">
@@ -570,7 +570,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-1.36</v>
+        <v>-13.58</v>
       </c>
     </row>
     <row r="7">
@@ -587,7 +587,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-1.83</v>
+        <v>-18.3</v>
       </c>
     </row>
     <row r="8">
@@ -604,7 +604,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-2.89</v>
+        <v>-28.88</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:12</t>
+    <t xml:space="preserve">2026-10-01 20:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:58</t>
+    <t xml:space="preserve">2026-10-02 13:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:25</t>
+    <t xml:space="preserve">2026-10-05 08:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
